--- a/Workplace Insights Survey (Excel-POWERBI-Python)/guidelines.xlsx
+++ b/Workplace Insights Survey (Excel-POWERBI-Python)/guidelines.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MBA - GUC\ABSK901\project2 - survey questionariry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MBA - GUC\ABSK901\project2 - survey questionariry\Analysis phase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9480FC95-5FCD-4C4F-BEA7-A60EC191E50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1364DD-0418-4094-9CEC-F74C4A6B1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B663F3A6-2759-438E-A866-BEE3DBED1DB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B663F3A6-2759-438E-A866-BEE3DBED1DB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Classification" sheetId="1" r:id="rId1"/>
     <sheet name="Design Sheet" sheetId="2" r:id="rId2"/>
     <sheet name="Questions Metadata" sheetId="3" r:id="rId3"/>
+    <sheet name="Demographics mapper" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="216">
   <si>
     <t>Q1</t>
   </si>
@@ -939,6 +940,48 @@
   </si>
   <si>
     <t>Productivity Factors - Simple Approval Process</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Prefer not to say</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Commercial / Sales</t>
+  </si>
+  <si>
+    <t>Technology / Network</t>
+  </si>
+  <si>
+    <t>Customer Care</t>
+  </si>
+  <si>
+    <t>Support Functions (HR, Finance, Legal)</t>
+  </si>
+  <si>
+    <t>Data &amp; Analytics</t>
+  </si>
+  <si>
+    <t>Tenure</t>
+  </si>
+  <si>
+    <t>Less than 1 year</t>
+  </si>
+  <si>
+    <t>1 to 3 years</t>
+  </si>
+  <si>
+    <t>3 to 5 years</t>
+  </si>
+  <si>
+    <t>More than 5 years</t>
   </si>
 </sst>
 </file>
@@ -2053,6 +2096,39 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{19F326F0-2BF5-4A76-8C40-5E2CAE4A1CAF}" name="Table1" displayName="Table1" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{19F326F0-2BF5-4A76-8C40-5E2CAE4A1CAF}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{A521BB74-46ED-4A2A-ADB7-0D0B2D940BD7}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{3740E714-33FB-4FD5-B7CD-5F538E379B54}" name="Gender"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CEE7826B-D225-4F6C-BCD6-5BDB50E2AF70}" name="Table2" displayName="Table2" ref="E1:F6" totalsRowShown="0">
+  <autoFilter ref="E1:F6" xr:uid="{CEE7826B-D225-4F6C-BCD6-5BDB50E2AF70}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{6F20B7A7-C99C-4AE7-AA59-1896E0292DA5}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{98CE8056-0E05-401B-AAC5-07822E0B0F03}" name="Department"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{860F5BBF-9D72-4CBD-AA8C-1DA2F5B842F8}" name="Table3" displayName="Table3" ref="J1:K5" totalsRowShown="0">
+  <autoFilter ref="J1:K5" xr:uid="{860F5BBF-9D72-4CBD-AA8C-1DA2F5B842F8}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{0F950A1B-A97A-43AD-A495-02337E3A4B1E}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{BBE2BA43-6F73-4BD6-9486-6CFAB29B3FB9}" name="Tenure"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4087,4 +4163,127 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A151E047-C4BE-4AFD-BD66-FAFDD627640C}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>208</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Workplace Insights Survey (Excel-POWERBI-Python)/guidelines.xlsx
+++ b/Workplace Insights Survey (Excel-POWERBI-Python)/guidelines.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MBA - GUC\ABSK901\project2 - survey questionariry\Analysis phase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1364DD-0418-4094-9CEC-F74C4A6B1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DEBEDE-3F2F-4EAF-BB30-5F3124C65447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B663F3A6-2759-438E-A866-BEE3DBED1DB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B663F3A6-2759-438E-A866-BEE3DBED1DB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Classification" sheetId="1" r:id="rId1"/>
     <sheet name="Design Sheet" sheetId="2" r:id="rId2"/>
     <sheet name="Questions Metadata" sheetId="3" r:id="rId3"/>
     <sheet name="Demographics mapper" sheetId="4" r:id="rId4"/>
+    <sheet name="Open-ended Question" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="297">
   <si>
     <t>Q1</t>
   </si>
@@ -982,6 +983,249 @@
   </si>
   <si>
     <t>More than 5 years</t>
+  </si>
+  <si>
+    <t>Move to another department that better suits my skills</t>
+  </si>
+  <si>
+    <t>Internal Mobility</t>
+  </si>
+  <si>
+    <t>Help maintain easy environment with gaining knowledge</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Measure the efficiency by the number of tasks that were finished during the call.</t>
+  </si>
+  <si>
+    <t>Documented everything</t>
+  </si>
+  <si>
+    <t>Operational Efficiency</t>
+  </si>
+  <si>
+    <t>Process Standardization</t>
+  </si>
+  <si>
+    <t>Sufficient time to submit documents and drawings and also with no stress</t>
+  </si>
+  <si>
+    <t>Improve the culture</t>
+  </si>
+  <si>
+    <t>Belonging &amp; Culture</t>
+  </si>
+  <si>
+    <t>Communciation within your own team is not productive,unnecessary side talks leads to confusion. Overall if you have a supportive team that can have your back will give you the opportunity even for personal growth</t>
+  </si>
+  <si>
+    <t>Company environment</t>
+  </si>
+  <si>
+    <t>The global communication</t>
+  </si>
+  <si>
+    <t>Facilitate and increase ways of communication</t>
+  </si>
+  <si>
+    <t>The work environment</t>
+  </si>
+  <si>
+    <t>Need to work in agile</t>
+  </si>
+  <si>
+    <t>🤷🏻‍♂️</t>
+  </si>
+  <si>
+    <t>General/Satisfied</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>No thing</t>
+  </si>
+  <si>
+    <t>Nothing, tbh</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>Increase team gathering to make future communications easier</t>
+  </si>
+  <si>
+    <t>Team Spirit</t>
+  </si>
+  <si>
+    <t>Add more resources</t>
+  </si>
+  <si>
+    <t>I guess to recruit more employees, clear defined tasks for each team</t>
+  </si>
+  <si>
+    <t>Work Pressure</t>
+  </si>
+  <si>
+    <t>communities</t>
+  </si>
+  <si>
+    <t>Social Belonging</t>
+  </si>
+  <si>
+    <t>Flexible hours</t>
+  </si>
+  <si>
+    <t>The old school concept</t>
+  </si>
+  <si>
+    <t>Culture Innovation</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Operational Structure</t>
+  </si>
+  <si>
+    <t>Alot</t>
+  </si>
+  <si>
+    <t>High Constructive Feedback</t>
+  </si>
+  <si>
+    <t>Working hours</t>
+  </si>
+  <si>
+    <t>More engagement</t>
+  </si>
+  <si>
+    <t>Focus on the clarity and technical debts</t>
+  </si>
+  <si>
+    <t>Strategic Clarity &amp; Objectives</t>
+  </si>
+  <si>
+    <t>Clearer KPIs</t>
+  </si>
+  <si>
+    <t>Providing development Plan for every one</t>
+  </si>
+  <si>
+    <t>well Organized tasks</t>
+  </si>
+  <si>
+    <t>Put clear rules &amp; the team must follow</t>
+  </si>
+  <si>
+    <t>To make work future plans more clear</t>
+  </si>
+  <si>
+    <t>having monthly plan</t>
+  </si>
+  <si>
+    <t>To have a clear structure and reasonable, well-planned tasms</t>
+  </si>
+  <si>
+    <t>Strategic Vision</t>
+  </si>
+  <si>
+    <t>Letting them do the time estimates and stop forcing unrealistic goals and expectations</t>
+  </si>
+  <si>
+    <t>Be open about the long term goals and how to reach the next step in my career path</t>
+  </si>
+  <si>
+    <t>More recognition of contributions and strong support for training and professional growth</t>
+  </si>
+  <si>
+    <t>Coaching &amp; Support</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>Leadership Support</t>
+  </si>
+  <si>
+    <t>To be aware of technicality more</t>
+  </si>
+  <si>
+    <t>More clarity and career guidance from leadership</t>
+  </si>
+  <si>
+    <t>Supporting and be part of each others work</t>
+  </si>
+  <si>
+    <t>Professional leadership</t>
+  </si>
+  <si>
+    <t>More solid guidelines &amp; Managerial support</t>
+  </si>
+  <si>
+    <t>Bi-daily meetings</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>meeting in person every 2 weeks</t>
+  </si>
+  <si>
+    <t>it's important to make a meeting frequently to solve the problems ,and to bring a new ideas to for a best system</t>
+  </si>
+  <si>
+    <t>More courses related to thw field</t>
+  </si>
+  <si>
+    <t>Personal Investment</t>
+  </si>
+  <si>
+    <t>Growth opportunities</t>
+  </si>
+  <si>
+    <t>Every role has its own responsibilities, not all roles do everything regardless Junior or Senior</t>
+  </si>
+  <si>
+    <t>transparency</t>
+  </si>
+  <si>
+    <t>Clear vision and SLA. Structured process to facilitate daily tasks.</t>
+  </si>
+  <si>
+    <t>having a clear team roadmap would make the work more impactful. Defining structured goals aligned with that roadmap, along with ensuring the team is properly trained before setting expectations, would help improve performance and reduce gaps. In addition, continuous technical guidance and support would enable the team to grow more confidently and deliver higher-quality results consistently</t>
+  </si>
+  <si>
+    <t>Regarding my daily work, I think the management need to think more about tasks distribution as it's not equally distributed and this lead to having a employees with no assigned tasks and others loaded.</t>
+  </si>
+  <si>
+    <t>Task Distribution</t>
+  </si>
+  <si>
+    <t>vote for decisions</t>
+  </si>
+  <si>
+    <t>Empowered Decision Making</t>
+  </si>
+  <si>
+    <t>To be more firm</t>
+  </si>
+  <si>
+    <t>Managerial Assertiveness</t>
+  </si>
+  <si>
+    <t>Less micromanagement for juniors</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Result oriented</t>
+  </si>
+  <si>
+    <t>Performance Culture</t>
   </si>
 </sst>
 </file>
@@ -4286,4 +4530,702 @@
     <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB3F610-A770-42BE-8F16-80FEC0C2ED2E}">
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>242</v>
+      </c>
+      <c r="B23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" t="s">
+        <v>245</v>
+      </c>
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>249</v>
+      </c>
+      <c r="B27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>251</v>
+      </c>
+      <c r="B28" t="s">
+        <v>252</v>
+      </c>
+      <c r="C28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" t="s">
+        <v>256</v>
+      </c>
+      <c r="C33" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" t="s">
+        <v>256</v>
+      </c>
+      <c r="C35" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>262</v>
+      </c>
+      <c r="B37" t="s">
+        <v>256</v>
+      </c>
+      <c r="C37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" t="s">
+        <v>264</v>
+      </c>
+      <c r="C38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>265</v>
+      </c>
+      <c r="B39" t="s">
+        <v>256</v>
+      </c>
+      <c r="C39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>266</v>
+      </c>
+      <c r="B40" t="s">
+        <v>264</v>
+      </c>
+      <c r="C40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>267</v>
+      </c>
+      <c r="B41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>269</v>
+      </c>
+      <c r="B42" t="s">
+        <v>270</v>
+      </c>
+      <c r="C42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>271</v>
+      </c>
+      <c r="B43" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>272</v>
+      </c>
+      <c r="B44" t="s">
+        <v>270</v>
+      </c>
+      <c r="C44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" t="s">
+        <v>270</v>
+      </c>
+      <c r="C45" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>274</v>
+      </c>
+      <c r="B46" t="s">
+        <v>270</v>
+      </c>
+      <c r="C46" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>275</v>
+      </c>
+      <c r="B47" t="s">
+        <v>270</v>
+      </c>
+      <c r="C47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>276</v>
+      </c>
+      <c r="B48" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>278</v>
+      </c>
+      <c r="B49" t="s">
+        <v>277</v>
+      </c>
+      <c r="C49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" t="s">
+        <v>277</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>277</v>
+      </c>
+      <c r="B51" t="s">
+        <v>277</v>
+      </c>
+      <c r="C51" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>280</v>
+      </c>
+      <c r="B52" t="s">
+        <v>281</v>
+      </c>
+      <c r="C52" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>283</v>
+      </c>
+      <c r="B54" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>284</v>
+      </c>
+      <c r="B55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>285</v>
+      </c>
+      <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>287</v>
+      </c>
+      <c r="B58" t="s">
+        <v>288</v>
+      </c>
+      <c r="C58" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>289</v>
+      </c>
+      <c r="B59" t="s">
+        <v>290</v>
+      </c>
+      <c r="C59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>291</v>
+      </c>
+      <c r="B60" t="s">
+        <v>292</v>
+      </c>
+      <c r="C60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>293</v>
+      </c>
+      <c r="B61" t="s">
+        <v>294</v>
+      </c>
+      <c r="C61" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>295</v>
+      </c>
+      <c r="B62" t="s">
+        <v>296</v>
+      </c>
+      <c r="C62" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Workplace Insights Survey (Excel-POWERBI-Python)/guidelines.xlsx
+++ b/Workplace Insights Survey (Excel-POWERBI-Python)/guidelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MBA - GUC\ABSK901\project2 - survey questionariry\Analysis phase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DEBEDE-3F2F-4EAF-BB30-5F3124C65447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8F6397-80E3-4CB8-97E8-0109B73D48DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B663F3A6-2759-438E-A866-BEE3DBED1DB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{B663F3A6-2759-438E-A866-BEE3DBED1DB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Classification" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Questions Metadata" sheetId="3" r:id="rId3"/>
     <sheet name="Demographics mapper" sheetId="4" r:id="rId4"/>
     <sheet name="Open-ended Question" sheetId="5" r:id="rId5"/>
+    <sheet name="Dim Multiple choices" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="319">
   <si>
     <t>Q1</t>
   </si>
@@ -1227,12 +1228,78 @@
   <si>
     <t>Performance Culture</t>
   </si>
+  <si>
+    <t>Extremely well</t>
+  </si>
+  <si>
+    <t>Never</t>
+  </si>
+  <si>
+    <t>Rarely</t>
+  </si>
+  <si>
+    <t>Sometimes</t>
+  </si>
+  <si>
+    <t>Often</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear Path </t>
+  </si>
+  <si>
+    <t>Steady Contribution</t>
+  </si>
+  <si>
+    <t>Unsure of Direction</t>
+  </si>
+  <si>
+    <t>Reatched Plateau</t>
+  </si>
+  <si>
+    <t>Tasks &amp; Autonomy</t>
+  </si>
+  <si>
+    <t>Team Collaboration</t>
+  </si>
+  <si>
+    <t>Learning &amp; Development</t>
+  </si>
+  <si>
+    <t>Fullfillment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth </t>
+  </si>
+  <si>
+    <t>Job Search</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Well-Being</t>
+  </si>
+  <si>
+    <t>Not Well</t>
+  </si>
+  <si>
+    <t>Somewhat</t>
+  </si>
+  <si>
+    <t>Adequately</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1312,6 +1379,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1327,7 +1413,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1381,11 +1467,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1432,6 +1604,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5228,4 +5421,236 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0815B825-6B33-4464-91E3-C783324D79D9}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1" s="31"/>
+    </row>
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="25">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="25">
+        <v>2</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="25">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="25">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="B8" s="31"/>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="25">
+        <v>1</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="25">
+        <v>2</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="25">
+        <v>3</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="25">
+        <v>4</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="B16" s="31"/>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="25">
+        <v>1</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="25">
+        <v>2</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="25">
+        <v>3</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="25">
+        <v>4</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B25" s="31"/>
+    </row>
+    <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="25">
+        <v>1</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="25">
+        <v>2</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="25">
+        <v>3</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="25">
+        <v>4</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="B32" s="31"/>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="25">
+        <v>1</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="25">
+        <v>2</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A32:B32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>